--- a/output/pdf_financials_xlsx/SEVA.xlsx
+++ b/output/pdf_financials_xlsx/SEVA.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001944</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.099314</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001944</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.099314</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.003736</v>
+        <v>0.001792</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.120282</v>
+        <v>0.020968</v>
       </c>
     </row>
     <row r="49">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/SEVA.xlsx
+++ b/output/pdf_financials_xlsx/SEVA.xlsx
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.000125</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.019176</v>
       </c>
     </row>
     <row r="102">
@@ -2608,7 +2608,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>0.000125</v>
       </c>
